--- a/mock_answer_key_template.xlsx
+++ b/mock_answer_key_template.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer Key" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +26,21 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,16 +424,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Question No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Correct Option</t>
         </is>
@@ -445,6 +460,102 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PDF mapping</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PDF page 1 = Question No 1, page 2 = Question No 2, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Use only A, B, C or D.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Parts</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>This answer key is for MAT and Arithmetic PDF uploads.</t>
         </is>
       </c>
     </row>
